--- a/data/trans_orig/IP1020-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1020-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49655</t>
+          <t>49618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55334</t>
+          <t>55973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107256</t>
+          <t>107483</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112200</t>
+          <t>112198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5412</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97890</t>
+          <t>98263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104664</t>
+          <t>104072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>204923</t>
+          <t>204907</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>75318</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150437</t>
+          <t>150345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38643</t>
+          <t>38583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82824</t>
+          <t>84109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52455</t>
+          <t>51761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111329</t>
+          <t>111733</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124054</t>
+          <t>124967</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>132406</t>
+          <t>131745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>259477</t>
+          <t>259121</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>480</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152596</t>
+          <t>152379</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>157275</t>
+          <t>157276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>158540</t>
+          <t>158704</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163577</t>
+          <t>163578</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>313592</t>
+          <t>313490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>320553</t>
+          <t>320505</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>670728</t>
+          <t>670333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>678504</t>
+          <t>678439</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>710418</t>
+          <t>711119</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>719424</t>
+          <t>719393</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1384823</t>
+          <t>1385165</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1396757</t>
+          <t>1396457</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8803</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>46152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52229</t>
+          <t>52269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55997</t>
+          <t>54958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60146</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104922</t>
+          <t>104144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>111936</t>
+          <t>111778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5756</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98957</t>
+          <t>99666</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107858</t>
+          <t>107870</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>209096</t>
+          <t>209290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>215229</t>
+          <t>215225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57933</t>
+          <t>57174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65436</t>
+          <t>65464</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66057</t>
+          <t>66878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126731</t>
+          <t>126413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>135696</t>
+          <t>135426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71347</t>
+          <t>71936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77194</t>
+          <t>76248</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>151502</t>
+          <t>151265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159211</t>
+          <t>159190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40137</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42228</t>
+          <t>42565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84925</t>
+          <t>85002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>462</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50539</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55526</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52873</t>
+          <t>52191</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59441</t>
+          <t>59471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105780</t>
+          <t>106850</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>113986</t>
+          <t>114060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7513</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>131205</t>
+          <t>131731</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>137999</t>
+          <t>137414</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142809</t>
+          <t>141676</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>276823</t>
+          <t>276158</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283024</t>
+          <t>283069</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>161286</t>
+          <t>160968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167141</t>
+          <t>167433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330480</t>
+          <t>330462</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>335429</t>
+          <t>335431</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38533</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>680452</t>
+          <t>681158</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>694716</t>
+          <t>695228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>731087</t>
+          <t>731200</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>742209</t>
+          <t>742211</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1416537</t>
+          <t>1415065</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1434666</t>
+          <t>1433745</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55304</t>
+          <t>54972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60718</t>
+          <t>60692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118080</t>
+          <t>118142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96703</t>
+          <t>96420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>102669</t>
+          <t>102697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102791</t>
+          <t>102824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108973</t>
+          <t>108959</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>201195</t>
+          <t>201283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>210335</t>
+          <t>210447</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>2718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66543</t>
+          <t>66563</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132913</t>
+          <t>134018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73416</t>
+          <t>73266</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74718</t>
+          <t>75155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80517</t>
+          <t>80518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149783</t>
+          <t>150294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>156944</t>
+          <t>156943</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39810</t>
+          <t>39707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86056</t>
+          <t>86434</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4178</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53561</t>
+          <t>54264</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108631</t>
+          <t>106636</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132248</t>
+          <t>133181</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>140142</t>
+          <t>139586</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>275243</t>
+          <t>275042</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280795</t>
+          <t>280746</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158938</t>
+          <t>158989</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>163725</t>
+          <t>163723</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161959</t>
+          <t>162669</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>169602</t>
+          <t>169607</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>324378</t>
+          <t>323845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>332558</t>
+          <t>332334</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19103</t>
+          <t>19954</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>688933</t>
+          <t>689137</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>698911</t>
+          <t>699025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>725741</t>
+          <t>724890</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>737586</t>
+          <t>737187</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1418705</t>
+          <t>1418053</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1433877</t>
+          <t>1433487</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76300</t>
+          <t>75597</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147816</t>
+          <t>149229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9682</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9919</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>117157</t>
+          <t>116607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125465</t>
+          <t>125420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117677</t>
+          <t>117656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126099</t>
+          <t>126149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>239310</t>
+          <t>238830</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>249882</t>
+          <t>250493</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>494</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4389</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53879</t>
+          <t>53552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57769</t>
+          <t>57774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60277</t>
+          <t>60060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65958</t>
+          <t>65910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>116054</t>
+          <t>115350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123391</t>
+          <t>122961</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>8330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9794</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60234</t>
+          <t>61813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138484</t>
+          <t>139172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>147446</t>
+          <t>147414</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>376</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3577</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>346</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34150</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36092</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40364</t>
+          <t>40373</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69520</t>
+          <t>69567</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74204</t>
+          <t>74094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41844</t>
+          <t>42602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51283</t>
+          <t>51432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>55812</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96053</t>
+          <t>95584</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101441</t>
+          <t>101354</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3953</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14290</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>17597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>11628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26430</t>
+          <t>26661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>110218</t>
+          <t>111436</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>120555</t>
+          <t>120565</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139518</t>
+          <t>138415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150784</t>
+          <t>150392</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>254090</t>
+          <t>253859</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>268842</t>
+          <t>268892</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>918</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>125565</t>
+          <t>124614</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>130972</t>
+          <t>130701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149361</t>
+          <t>149498</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155940</t>
+          <t>155942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>277076</t>
+          <t>277356</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>285990</t>
+          <t>286060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32889</t>
+          <t>31410</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>34309</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36197</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>59866</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>632451</t>
+          <t>633930</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>649727</t>
+          <t>650597</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>727204</t>
+          <t>727663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>744543</t>
+          <t>744859</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1367446</t>
+          <t>1367639</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1391115</t>
+          <t>1390731</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
